--- a/교육생관리/교육생구글시트용.xlsx
+++ b/교육생관리/교육생구글시트용.xlsx
@@ -2,71 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="1">
     <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="2"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="돋움"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Malgun Gothic"/>
-      <family val="2"/>
-      <color theme="3" tint="0.1499374370555742"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Malgun Gothic"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color theme="3" tint="0.1499374370555742"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.0499893185216834"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -74,88 +42,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="왼쪽 정렬된 표 세부 정보" xfId="1"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.5999633777886288"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.5999633777886288"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.5999633777886288"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -228,7 +125,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -238,44 +135,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -302,32 +199,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -354,24 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -383,162 +244,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -549,312 +414,285 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
-  <cols>
-    <col width="15" customWidth="1" style="4" min="2" max="2"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>개강반</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="33" customHeight="1" s="4">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>조현영</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>2026.01.14</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="33" customHeight="1" s="4">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>강봉구</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>2026.01.14</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="33" customHeight="1" s="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>송지현</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>2026.01.14</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="33" customHeight="1" s="4">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>안재현</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>2026.01.14</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="33" customHeight="1" s="4">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>박희연</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>2026.01.14</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="33" customHeight="1" s="4">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>안경선</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>2026.01.14</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="33" customHeight="1" s="4">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>김태리</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>2026.01.14</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="33" customHeight="1" s="4">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>곽미연</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025.10.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>조소연</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>2026.03.11</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="33" customHeight="1" s="4">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>민경준</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>2025.03.11</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="33" customHeight="1" s="4">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>이소희</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2025.11.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="33" customHeight="1" s="4">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026.07.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>오혜성</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026.02.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>김주현</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>2026.03.11</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="33" customHeight="1" s="4">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>박선홍</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2026.03.11</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="33" customHeight="1" s="4">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>이수연</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>2026.03.11</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1" s="4">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>이지연</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>2026.03.11</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="33" customHeight="1" s="4">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>김리아</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026.04.15</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="33" customHeight="1" s="4">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>권민정</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>2026.03.11</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="0" t="inlineStr">
-        <is>
-          <t>김보영</t>
-        </is>
-      </c>
-      <c r="B18" s="0" t="inlineStr">
-        <is>
-          <t>2026.05.13</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0" t="inlineStr">
-        <is>
-          <t>강은경</t>
-        </is>
-      </c>
-      <c r="B19" s="0" t="inlineStr">
-        <is>
-          <t>2026.05.13</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
-      <c r="A20" s="0" t="inlineStr">
-        <is>
-          <t>박유리</t>
-        </is>
-      </c>
-      <c r="B20" s="0" t="inlineStr">
-        <is>
-          <t>2026.05.13</t>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>이혜민</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026.04.15</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>이혜민</t>
+          <t>김보영</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026.04.15</t>
+          <t>2026.05.13</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>곽미연</t>
+          <t>강은경</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025.10.22</t>
+          <t>2026.05.13</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>오혜성</t>
+          <t>박유리</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026.02.</t>
+          <t>2026.05.13</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A17 B11:B17">
-    <cfRule type="expression" priority="5" dxfId="1">
-      <formula>$I2=1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="6" dxfId="0">
-      <formula>"If(blnBinNo=""True"")"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B8">
-    <cfRule type="expression" priority="3" dxfId="1">
-      <formula>$I2=1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="0">
-      <formula>"If(blnBinNo=""True"")"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9:B10">
-    <cfRule type="expression" priority="1" dxfId="1">
-      <formula>$I9=1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="0">
-      <formula>"If(blnBinNo=""True"")"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/교육생관리/교육생구글시트용.xlsx
+++ b/교육생관리/교육생구글시트용.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,19 +563,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>오혜성</t>
+          <t>김주현</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026.02.</t>
+          <t>2026.03.11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>김주현</t>
+          <t>박선홍</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>박선홍</t>
+          <t>이수연</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>이수연</t>
+          <t>이지연</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -611,55 +611,55 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>이지연</t>
+          <t>김리아</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026.03.11</t>
+          <t>2026.04.15</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>김리아</t>
+          <t>권민정</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026.04.15</t>
+          <t>2026.03.11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>권민정</t>
+          <t>이혜민</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026.03.11</t>
+          <t>2026.04.15</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>이혜민</t>
+          <t>김보영</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026.04.15</t>
+          <t>2026.05.13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>김보영</t>
+          <t>강은경</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -671,22 +671,10 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>강은경</t>
+          <t>박유리</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
-        <is>
-          <t>2026.05.13</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>박유리</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
         <is>
           <t>2026.05.13</t>
         </is>

--- a/교육생관리/교육생구글시트용.xlsx
+++ b/교육생관리/교육생구글시트용.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,6 +680,18 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>안희진</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026.05.13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/교육생관리/교육생구글시트용.xlsx
+++ b/교육생관리/교육생구글시트용.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,6 +692,30 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>홍미정</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026.05.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>홍순정</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026.05.13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/교육생관리/교육생구글시트용.xlsx
+++ b/교육생관리/교육생구글시트용.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +427,46 @@
           <t>개강반</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>개강반차수1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>개강반차수2</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>개강반차수3</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>실습</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>실습2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -436,7 +476,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2년제</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025.08.06</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>2026.01.14</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>브니</t>
         </is>
       </c>
     </row>
@@ -448,7 +520,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3년제</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025.08.06</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026.01.14</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>브니</t>
         </is>
       </c>
     </row>
@@ -460,7 +564,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2년제</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025.08.06</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026.01.14</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>브니</t>
         </is>
       </c>
     </row>
@@ -472,7 +608,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>고졸</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025.08.06</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026.01.14</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>브니</t>
         </is>
       </c>
     </row>
@@ -484,7 +652,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4년제</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025.08.06</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026.01.14</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>브니</t>
         </is>
       </c>
     </row>
@@ -496,7 +696,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.01.14</t>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>고졸</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025.08.06</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2025.12.10</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>브니</t>
         </is>
       </c>
     </row>
@@ -508,7 +740,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026.01.14</t>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2년제</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025.08.06</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2025.12.10</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>브니</t>
         </is>
       </c>
     </row>
@@ -523,6 +787,38 @@
           <t>2025.10.22</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4년제</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025.10.22</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>희망자격증 2개</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>희망자격증 2개</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -532,7 +828,43 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4년제</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025.10.22</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026.03.11</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>브니</t>
         </is>
       </c>
     </row>
@@ -544,9 +876,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025.03.11</t>
-        </is>
-      </c>
+          <t>2026.04.15</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2년제</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025.10.22</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026.04.15</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>분할결제
+35/35/35</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -559,6 +924,38 @@
           <t>2026.07.15</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>고졸</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025.11.12</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026.03.11</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026.07.15</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1100000</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>브니</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -568,7 +965,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>2026.07.15</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>보육교사,2년제</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>2026.03.11</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026.07.15</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>770000</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>보육교사O</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>브니</t>
         </is>
       </c>
     </row>
@@ -583,6 +1012,34 @@
           <t>2026.03.11</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>대졸</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026.03.11</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>33/33/34분할결제</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>브니</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -592,9 +1049,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>2026.09.09</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>대졸</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>2026.03.11</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026.09.09</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>800000</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>보육교사O</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -604,9 +1089,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>2026.07.15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>전문대졸</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>2026.03.11</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026.07.15</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>800000</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>보육교사O</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -616,9 +1129,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>2026.12.16</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>고졸</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>2026.04.15</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026.09.09</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026.12.16</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1100000</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -631,6 +1172,30 @@
           <t>2026.03.11</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026.03.11</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>건수인정</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>교육원에서자체처리</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -640,7 +1205,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>2026.12.16</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>전문대졸</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>2026.04.15</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026.09.09</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026.12.16</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>브니</t>
         </is>
       </c>
     </row>
@@ -652,7 +1245,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>2026.09.09</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>고졸</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>2026.05.13</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026.09.09</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1050000</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>브니</t>
         </is>
       </c>
     </row>
@@ -664,7 +1285,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>2026.09.09</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>대졸</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>2026.05.13</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026.09.09</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>950000</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>브니</t>
         </is>
       </c>
     </row>
@@ -676,7 +1325,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>2026.09.09</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>전문대졸</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>2026.05.13</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026.09.09</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>950000</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>브니</t>
         </is>
       </c>
     </row>
@@ -688,7 +1365,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>2026.09.09</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>전문대졸</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>2026.05.13</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026.09.09</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>950000</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>브니</t>
         </is>
       </c>
     </row>
@@ -700,7 +1405,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>2026.09.09</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>대졸</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>2026.05.13</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026.09.09</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>950000</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>브니</t>
         </is>
       </c>
     </row>
@@ -712,7 +1449,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>2026.09.09</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>대졸</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>2026.05.13</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026.09.09</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>950000</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>브니</t>
         </is>
       </c>
     </row>
